--- a/risk_matrix/risk_matrix.xlsx
+++ b/risk_matrix/risk_matrix.xlsx
@@ -503,13 +503,13 @@
       <c r="B2" s="3" t="inlineStr"/>
       <c r="C2" s="3" t="inlineStr"/>
       <c r="D2" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>1</v>
@@ -522,17 +522,17 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>3</v>
@@ -548,16 +548,16 @@
         <v>4</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
     </row>
@@ -567,13 +567,11 @@
           <t>Coordinated low-level malicious attack</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr"/>
@@ -589,14 +587,12 @@
         <v>1</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>2</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
@@ -606,19 +602,19 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>7</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>1</v>

--- a/risk_matrix/risk_matrix.xlsx
+++ b/risk_matrix/risk_matrix.xlsx
@@ -503,10 +503,10 @@
       <c r="B2" s="3" t="inlineStr"/>
       <c r="C2" s="3" t="inlineStr"/>
       <c r="D2" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>9</v>
@@ -522,20 +522,20 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -545,19 +545,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
     </row>
@@ -570,9 +570,7 @@
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr"/>
     </row>
@@ -584,15 +582,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr"/>
       <c r="C6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" s="3" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="G6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>1</v>

--- a/risk_matrix/risk_matrix.xlsx
+++ b/risk_matrix/risk_matrix.xlsx
@@ -509,7 +509,7 @@
         <v>11</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>1</v>
@@ -522,17 +522,17 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>2</v>
@@ -548,16 +548,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
     </row>
@@ -570,7 +570,9 @@
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
+      <c r="E5" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr"/>
     </row>
@@ -580,15 +582,17 @@
           <t>Low-level malicious attack</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr"/>
+      <c r="B6" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="C6" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>2</v>
@@ -602,22 +606,22 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/risk_matrix/risk_matrix.xlsx
+++ b/risk_matrix/risk_matrix.xlsx
@@ -522,17 +522,17 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="4" t="n">
         <v>19</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>2</v>
@@ -548,16 +548,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
     </row>
@@ -589,10 +589,10 @@
         <v>4</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>2</v>
@@ -606,22 +606,22 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/risk_matrix/risk_matrix.xlsx
+++ b/risk_matrix/risk_matrix.xlsx
@@ -509,7 +509,7 @@
         <v>11</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>1</v>
@@ -522,17 +522,17 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>2</v>
@@ -551,13 +551,13 @@
         <v>20</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
     </row>
@@ -586,16 +586,16 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>11</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
     </row>
@@ -609,16 +609,16 @@
         <v>11</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>16</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>3</v>

--- a/risk_matrix/risk_matrix.xlsx
+++ b/risk_matrix/risk_matrix.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Risk Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Matrix" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,11 +27,11 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -68,10 +68,10 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -503,13 +503,13 @@
       <c r="B2" s="3" t="inlineStr"/>
       <c r="C2" s="3" t="inlineStr"/>
       <c r="D2" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2" s="4" t="n">
         <v>11</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>7</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>1</v>
@@ -522,20 +522,22 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="D3" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -545,19 +547,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
     </row>
@@ -583,19 +585,19 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
     </row>
@@ -606,22 +608,22 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="D7" s="4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
